--- a/data/Company_Master.xlsx
+++ b/data/Company_Master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apparelme-my.sharepoint.com/personal/138925_appareluae_com/Documents/LS Retail - Masters/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apparelme-my.sharepoint.com/personal/138925_appareluae_com/Documents/F&amp;B Sales Dashboard - Project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{435EB669-0B53-404B-9887-A50634BD41E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ECD0FA2-82FE-4E7B-AC6A-71F1163F2363}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{435EB669-0B53-404B-9887-A50634BD41E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{411A54B6-05B5-44C9-A2C1-E4F389D59D0B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B76173A0-443A-4532-A0AF-4EB7DE1D271E}"/>
+    <workbookView xWindow="8840" yWindow="2880" windowWidth="11760" windowHeight="6160" xr2:uid="{B76173A0-443A-4532-A0AF-4EB7DE1D271E}"/>
   </bookViews>
   <sheets>
     <sheet name="Company_Master_tbl" sheetId="1" r:id="rId1"/>
@@ -42,21 +42,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
-    <t>Company_Code</t>
-  </si>
-  <si>
-    <t>Company_Name</t>
-  </si>
-  <si>
-    <t>Company_TRN_No</t>
-  </si>
-  <si>
-    <t>Company_Address</t>
-  </si>
-  <si>
-    <t>Company_Country_Code</t>
-  </si>
-  <si>
     <t>Apparel International LLC</t>
   </si>
   <si>
@@ -78,9 +63,6 @@
     <t>Sprinklez For Restaurant Management WLL</t>
   </si>
   <si>
-    <t>Company_Sr_No</t>
-  </si>
-  <si>
     <t>OM</t>
   </si>
   <si>
@@ -97,6 +79,24 @@
   </si>
   <si>
     <t>KW</t>
+  </si>
+  <si>
+    <t>company_sr_no</t>
+  </si>
+  <si>
+    <t>company_code</t>
+  </si>
+  <si>
+    <t>company_name</t>
+  </si>
+  <si>
+    <t>company_trn_no</t>
+  </si>
+  <si>
+    <t>company_addr</t>
+  </si>
+  <si>
+    <t>company_country_code</t>
   </si>
 </sst>
 </file>
@@ -466,22 +466,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -492,10 +492,10 @@
         <v>14001</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -506,10 +506,10 @@
         <v>15007</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -520,10 +520,10 @@
         <v>16001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -534,10 +534,10 @@
         <v>12002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -548,10 +548,10 @@
         <v>22003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -562,10 +562,10 @@
         <v>22006</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -576,10 +576,10 @@
         <v>13010</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
